--- a/data/trans_dic/P45C_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,23</t>
+          <t>1,0; 3,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,87</t>
+          <t>0,43; 1,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,24</t>
+          <t>0,42; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,36</t>
+          <t>1,09; 3,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,08</t>
+          <t>0,52; 2,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,24</t>
+          <t>1,08; 3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,34; 2,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,68</t>
+          <t>0,59; 1,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,32</t>
+          <t>0,89; 2,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,53</t>
+          <t>0,79; 2,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,33</t>
+          <t>0,75; 2,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,54</t>
+          <t>0,29; 1,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,6</t>
+          <t>0,61; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,59</t>
+          <t>0,87; 2,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,82; 2,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,17</t>
+          <t>0,69; 2,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,45</t>
+          <t>1,07; 2,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,13</t>
+          <t>1,03; 2,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,11</t>
+          <t>0,9; 2,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,53</t>
+          <t>0,61; 1,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,31</t>
+          <t>0,95; 2,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,42</t>
+          <t>1,62; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,42</t>
+          <t>0,66; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,93</t>
+          <t>0,83; 2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,96</t>
+          <t>1,15; 3,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,09</t>
+          <t>1,57; 4,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,61</t>
+          <t>0,36; 1,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,37</t>
+          <t>0,65; 2,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,0</t>
+          <t>0,75; 3,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,67</t>
+          <t>1,88; 3,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,74</t>
+          <t>0,65; 1,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,2</t>
+          <t>0,96; 2,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,96</t>
+          <t>1,17; 2,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,16</t>
+          <t>1,3; 3,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,34</t>
+          <t>0,29; 1,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,15</t>
+          <t>0,27; 1,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,71</t>
+          <t>0,95; 2,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,32</t>
+          <t>1,44; 3,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,05</t>
+          <t>1,33; 3,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,61</t>
+          <t>0,47; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,1</t>
+          <t>0,29; 1,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,93</t>
+          <t>1,55; 2,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,02</t>
+          <t>0,98; 2,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,17</t>
+          <t>0,45; 1,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,62</t>
+          <t>0,73; 1,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,19</t>
+          <t>1,28; 2,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,75</t>
+          <t>0,95; 1,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,32</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,16</t>
+          <t>1,15; 2,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,13</t>
+          <t>1,28; 2,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,06</t>
+          <t>1,17; 2,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,55</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,84</t>
+          <t>1,04; 1,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,05</t>
+          <t>1,37; 2,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,76</t>
+          <t>1,2; 1,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,8; 1,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,89</t>
+          <t>1,19; 1,86</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 10480</t>
+          <t>0; 8515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7056; 22548</t>
+          <t>6996; 21640</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2871; 12588</t>
+          <t>2923; 13221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2562; 14144</t>
+          <t>2622; 13839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 4812</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7767; 23323</t>
+          <t>7610; 23914</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3616; 13968</t>
+          <t>3484; 13777</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6909; 21836</t>
+          <t>7291; 20872</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>947; 11023</t>
+          <t>952; 12157</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19134; 42076</t>
+          <t>18678; 40242</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7927; 22507</t>
+          <t>7881; 22182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12201; 30291</t>
+          <t>11571; 29527</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7807; 24279</t>
+          <t>7570; 23458</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7321; 23441</t>
+          <t>7595; 24677</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3036; 15615</t>
+          <t>2922; 15560</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7835; 30970</t>
+          <t>7224; 31553</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8526; 25033</t>
+          <t>8385; 24144</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8621; 24562</t>
+          <t>8350; 22817</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6655; 22510</t>
+          <t>7109; 23860</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9267; 23461</t>
+          <t>10234; 24441</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19156; 41013</t>
+          <t>19823; 41901</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19027; 42894</t>
+          <t>18267; 41473</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11700; 31286</t>
+          <t>12593; 32328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22249; 49648</t>
+          <t>20389; 49604</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11060; 29948</t>
+          <t>11000; 30153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5192; 18099</t>
+          <t>4967; 17944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5959; 21940</t>
+          <t>6207; 21897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7652; 27777</t>
+          <t>8097; 27518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10247; 27892</t>
+          <t>10703; 28149</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2069; 12334</t>
+          <t>2771; 13152</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5140; 18345</t>
+          <t>5044; 17953</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6532; 28001</t>
+          <t>6973; 28502</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25094; 49854</t>
+          <t>25603; 50210</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9735; 26337</t>
+          <t>9808; 26172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13427; 33544</t>
+          <t>14592; 34835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19253; 48469</t>
+          <t>19183; 47526</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12148; 29695</t>
+          <t>12190; 30908</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2786; 12666</t>
+          <t>2783; 13333</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1787; 10714</t>
+          <t>2523; 11003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9054; 25159</t>
+          <t>8777; 25431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14910; 34343</t>
+          <t>14864; 34015</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13056; 31762</t>
+          <t>13826; 33667</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4048; 16704</t>
+          <t>4845; 16236</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3012; 12005</t>
+          <t>3129; 12363</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30885; 57954</t>
+          <t>30694; 57536</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19013; 39988</t>
+          <t>19352; 40545</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8419; 23095</t>
+          <t>8903; 23493</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14572; 32680</t>
+          <t>14712; 33561</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41158; 71594</t>
+          <t>41915; 72746</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32497; 59551</t>
+          <t>32323; 60314</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20462; 44332</t>
+          <t>21110; 45565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38688; 74710</t>
+          <t>39776; 77503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42023; 71951</t>
+          <t>43297; 73097</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42517; 72634</t>
+          <t>41378; 72597</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28480; 54585</t>
+          <t>28262; 53496</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39338; 67432</t>
+          <t>38216; 67394</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92764; 135990</t>
+          <t>91197; 133070</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82646; 121592</t>
+          <t>82768; 124239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54591; 89984</t>
+          <t>55294; 91240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85001; 134634</t>
+          <t>84783; 132144</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,1</t>
+          <t>1,09; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,97</t>
+          <t>0,3; 1,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,19</t>
+          <t>0,43; 2,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,44</t>
+          <t>1,15; 3,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,06</t>
+          <t>0,41; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,09</t>
+          <t>0,97; 2,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,88</t>
+          <t>0,07; 0,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,89</t>
+          <t>1,37; 2,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,65</t>
+          <t>0,61; 1,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,26</t>
+          <t>0,83; 2,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,45</t>
+          <t>0,81; 2,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,45</t>
+          <t>0,73; 2,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,54</t>
+          <t>0,28; 1,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,65</t>
+          <t>1,05; 3,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,5</t>
+          <t>0,87; 2,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,23</t>
+          <t>0,89; 2,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,3</t>
+          <t>0,67; 2,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,55</t>
+          <t>1,04; 2,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,18</t>
+          <t>0,97; 2,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,04</t>
+          <t>0,98; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,58</t>
+          <t>0,59; 1,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,31</t>
+          <t>1,21; 2,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,45</t>
+          <t>1,61; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,39</t>
+          <t>0,68; 2,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,92</t>
+          <t>0,8; 2,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,92</t>
+          <t>1,15; 3,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,13</t>
+          <t>1,48; 3,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,71</t>
+          <t>0,29; 1,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,31</t>
+          <t>0,66; 2,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,06</t>
+          <t>1,6; 3,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,69</t>
+          <t>1,87; 3,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,73</t>
+          <t>0,66; 1,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,28</t>
+          <t>0,9; 2,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,91</t>
+          <t>1,61; 3,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,29</t>
+          <t>1,26; 3,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,41</t>
+          <t>0,3; 1,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,18</t>
+          <t>0,27; 1,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,74</t>
+          <t>0,96; 2,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,28</t>
+          <t>1,44; 3,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,24</t>
+          <t>1,24; 3,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,57</t>
+          <t>0,4; 1,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,13</t>
+          <t>0,31; 1,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,91</t>
+          <t>1,6; 2,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,04</t>
+          <t>0,96; 1,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,19</t>
+          <t>0,43; 1,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,66</t>
+          <t>0,74; 1,6</t>
         </is>
       </c>
     </row>
@@ -1224,19 +1224,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,23</t>
+          <t>1,27; 2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,77</t>
+          <t>0,94; 1,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,35</t>
+          <t>0,59; 1,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,24</t>
+          <t>1,25; 2,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,17</t>
+          <t>1,26; 2,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,06</t>
+          <t>1,18; 2,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,52</t>
+          <t>0,79; 1,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,84</t>
+          <t>1,2; 2,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,0</t>
+          <t>1,39; 2,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,79</t>
+          <t>1,14; 1,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,33</t>
+          <t>0,77; 1,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,86</t>
+          <t>1,32; 1,95</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>19338</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8515</t>
+          <t>0; 10322</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6996; 21640</t>
+          <t>7633; 22229</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2923; 13221</t>
+          <t>2016; 13387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2622; 13839</t>
+          <t>2932; 13901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 4878</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7610; 23914</t>
+          <t>7970; 24092</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3484; 13777</t>
+          <t>2772; 13577</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7291; 20872</t>
+          <t>7086; 20427</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>952; 12157</t>
+          <t>953; 12436</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18678; 40242</t>
+          <t>19127; 40540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7881; 22182</t>
+          <t>8237; 22090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11571; 29527</t>
+          <t>11814; 29717</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>37054</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7570; 23458</t>
+          <t>7770; 24822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7595; 24677</t>
+          <t>7360; 23267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2922; 15560</t>
+          <t>2853; 15638</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7224; 31553</t>
+          <t>10976; 32260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8385; 24144</t>
+          <t>8421; 24048</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8350; 22817</t>
+          <t>9076; 25346</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7109; 23860</t>
+          <t>6892; 22418</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10234; 24441</t>
+          <t>11089; 27461</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19823; 41901</t>
+          <t>18575; 41723</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18267; 41473</t>
+          <t>19942; 41843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12593; 32328</t>
+          <t>12050; 31810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20389; 49604</t>
+          <t>25669; 52669</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>38065</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11000; 30153</t>
+          <t>10929; 29862</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4967; 17944</t>
+          <t>5117; 18085</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6207; 21897</t>
+          <t>5967; 22075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8097; 27518</t>
+          <t>9243; 30258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10703; 28149</t>
+          <t>10098; 26246</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2771; 13152</t>
+          <t>2212; 12091</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5044; 17953</t>
+          <t>5151; 18098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6973; 28502</t>
+          <t>12935; 31256</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25603; 50210</t>
+          <t>25460; 50536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9808; 26172</t>
+          <t>9944; 25679</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14592; 34835</t>
+          <t>13691; 34294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19183; 47526</t>
+          <t>25859; 54464</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>23176</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12190; 30908</t>
+          <t>11800; 30999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2783; 13333</t>
+          <t>2850; 13379</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2523; 11003</t>
+          <t>2528; 10854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8777; 25431</t>
+          <t>9466; 25902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14864; 34015</t>
+          <t>14883; 33533</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13826; 33667</t>
+          <t>12931; 32138</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4845; 16236</t>
+          <t>4145; 15558</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3129; 12363</t>
+          <t>3444; 13095</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30694; 57536</t>
+          <t>31681; 58321</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19352; 40545</t>
+          <t>18986; 39295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8903; 23493</t>
+          <t>8507; 23808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14712; 33561</t>
+          <t>15578; 33747</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41915; 72746</t>
+          <t>41443; 72470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32323; 60314</t>
+          <t>31878; 59707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21110; 45565</t>
+          <t>19928; 43526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39776; 77503</t>
+          <t>44235; 80260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43297; 73097</t>
+          <t>42484; 72232</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41378; 72597</t>
+          <t>41573; 72617</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28262; 53496</t>
+          <t>27888; 52384</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38216; 67394</t>
+          <t>44932; 75935</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>91197; 133070</t>
+          <t>92113; 136039</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82768; 124239</t>
+          <t>79250; 120888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55294; 91240</t>
+          <t>53130; 88717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>84783; 132144</t>
+          <t>95811; 141205</t>
         </is>
       </c>
     </row>
